--- a/DateBase/orders/Nhat 48_2026-9-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-24.xlsx
@@ -521,6 +521,9 @@
       <c r="C11" t="str">
         <v>538_扁豆_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -579,7 +582,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01085155652050</v>
+        <v>01085155652055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,9 +525,90 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>816_山里红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>859_喷色小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>555_地服_kochia_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="C15" t="str" xml:space="preserve">
+        <v xml:space="preserve">405_小飞燕深蓝_ delphinium ballkleid
+dark blue_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>318_尤加利果_Eucalyptus pods_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F17" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3</v>
+      </c>
+      <c r="C18" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F19" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -582,7 +663,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01085155652055</v>
+        <v>0108515565205555510152186100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-24.xlsx
@@ -603,7 +603,7 @@
     </row>
     <row r="21">
       <c r="C21" t="str">
-        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-24.xlsx
@@ -605,6 +605,9 @@
       <c r="C21" t="str">
         <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -663,7 +666,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0108515565205555510152186100</v>
+        <v>01085155652055555101521861030</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -609,9 +609,92 @@
         <v>30</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>744_永生吊米深红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>653_大丽花 黑_undefined_undefined_5stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>802_烟花菊粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>592_进口春兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -666,7 +749,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01085155652055555101521861030</v>
+        <v>010851556520555551015218610301058156656100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-24.xlsx
@@ -691,6 +691,9 @@
       <c r="C31" t="str">
         <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -749,7 +752,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010851556520555551015218610301058156656100</v>
+        <v>010851556520555551015218610301058156656105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -695,9 +695,103 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>849_婚庆卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>6</v>
+      </c>
+      <c r="C34" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>7</v>
+      </c>
+      <c r="C40" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F41" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L42"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -752,7 +846,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010851556520555551015218610301058156656105</v>
+        <v>0108515565205555510152186103010581566561051013195865109710</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -438,12 +438,13 @@
         <v>TotalPrice</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>522_山归来绿_Smilax china_undefined_1bunch</v>
+        <v>7</v>
+      </c>
+      <c r="C2" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
       </c>
       <c r="F2" t="str">
         <v>10</v>
@@ -451,347 +452,31 @@
     </row>
     <row r="3">
       <c r="C3" t="str">
-        <v>885_杨梅树枝_undefined_undefined_1bunch</v>
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
       </c>
       <c r="F3" t="str">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>2</v>
-      </c>
       <c r="C4" t="str">
-        <v>341_南天竹绿_undefined_Nandina domestica Thunb._1bunch</v>
+        <v>126_绣球苹果绿_Hydrangea Garden Lace_Hydrangea L._1stem</v>
       </c>
       <c r="F4" t="str">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="str">
-        <v>348_万年青_undefined_undefined_1bunch</v>
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
       </c>
       <c r="F5" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" t="str">
-        <v>344_钢草_steal grass_Xanthorrhoea preissii Endl._1bunch</v>
-      </c>
-      <c r="F6" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" t="str">
-        <v>693_迎客豆_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F7" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
-      <c r="C8" t="str" xml:space="preserve">
-        <v xml:space="preserve">349_千层金绿_Melaleuca bracteata
-（dyed orange）_Melaleuca bracteata F.Muell._1bunch</v>
-      </c>
-      <c r="F8" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="C9" t="str">
-        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
-      </c>
-      <c r="F9" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" t="str">
-        <v>864_黄洋金边红色_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F10" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="str">
-        <v>538_扁豆_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F11" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" t="str">
-        <v>816_山里红_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F12" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" t="str">
-        <v>859_喷色小米果_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F13" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" t="str">
-        <v>555_地服_kochia_undefined_1bunch</v>
-      </c>
-      <c r="F14" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="C15" t="str" xml:space="preserve">
-        <v xml:space="preserve">405_小飞燕深蓝_ delphinium ballkleid
-dark blue_undefined_1bunch</v>
-      </c>
-      <c r="F15" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="str">
-        <v>318_尤加利果_Eucalyptus pods_undefined_1bunch</v>
-      </c>
-      <c r="F16" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="str">
-        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
-      </c>
-      <c r="F17" t="str">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3</v>
-      </c>
-      <c r="C18" t="str">
-        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
-      </c>
-      <c r="F18" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="str">
-        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
-      </c>
-      <c r="F19" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="str">
-        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
-      </c>
-      <c r="F20" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="str">
-        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F21" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="str">
-        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F22" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="str">
-        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F23" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="str">
-        <v>744_永生吊米深红_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F24" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>4</v>
-      </c>
-      <c r="C25" t="str">
-        <v>653_大丽花 黑_undefined_undefined_5stems</v>
-      </c>
-      <c r="F25" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>5</v>
-      </c>
-      <c r="C26" t="str">
-        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F26" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="str">
-        <v>802_烟花菊粉_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F27" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="str">
-        <v>592_进口春兰叶_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F28" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="str">
-        <v>447_黄金球_craspedia_undefined_1bunch</v>
-      </c>
-      <c r="F29" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="str">
-        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
-      </c>
-      <c r="F30" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="str">
-        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
-      </c>
-      <c r="F31" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="str">
-        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
-      </c>
-      <c r="F32" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="str">
-        <v>849_婚庆卢荀草_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F33" t="str">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>6</v>
-      </c>
-      <c r="C34" t="str">
-        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F34" t="str">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="str">
-        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F35" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="str">
-        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F36" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="str">
-        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F37" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="str">
-        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
-      </c>
-      <c r="F38" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="str">
-        <v>439_九星叶_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F39" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>7</v>
-      </c>
-      <c r="C40" t="str">
-        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F40" t="str">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="str">
-        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F41" t="str">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="str">
-        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F42" t="str">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -846,7 +531,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0108515565205555510152186103010581566561051013195865109710</v>
+        <v>010151510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -474,9 +474,36 @@
         <v>10</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>9</v>
+      </c>
+      <c r="C6" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
+      <c r="F6" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F7" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="str">
+        <v>540_糖棉_gomphocarpus fruticosus_undefined_1bunch</v>
+      </c>
+      <c r="F8" t="str">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -531,7 +558,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010151510</v>
+        <v>01015151015153</v>
       </c>
     </row>
   </sheetData>
